--- a/site/exports/uestc-economics-management.xlsx
+++ b/site/exports/uestc-economics-management.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,9 +452,9 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3个学位标签的获授状态unknown；单列年月语义未明，不补授位或学习起止。；亚利桑那同次访学止期2012-08与2012-09冲突，end=null，保留两处原文。；现职unknown与导航false；目录只证明列示归属。；本人正式论文导师、阶段师承均未找到可接受证据，不从合著、授课/指导资格推定。；作品作者年份仅官网原文；无出版社元数据外核与论文全文。；页面日期未显示，抓取时间不替代页面日期。；来源差异/限制：同一次亚利桑那访学的两处止期2012-08与2012-09并列保留，end=null，不拆为两次事件。；来源记载职业信息：职业角色：经济学与金融学系系主任。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：中级微观经济学；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；教学语言/方式：双语；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济学Ⅱ；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；课程标记：挑战性课程；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 论文写作与口头表达；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济学；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；教学对象：留学生；教学语言/方式：英语；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 高级宏观经济学；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；教学语言/方式：双语；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济研究方法；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 管理经济学；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；教学对象：留学生；教学语言/方式：英语；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济学前沿；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：博士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济管理研究方法；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：博士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；教学对象：留学生；教学语言/方式：英语；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 经济管理研究方法；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：博士研究生；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；项目标签：DoM；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | 管理经济学；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：MBA；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm | MBA论文写作；课程开发负责人；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：MBA；来源主张范围：既有已选事实容器的来源报告；不作独立身份、任职或资格认证；时间限制：沿用本条既有时段与限制；未明示的起止日期仍未知；来源ID：new-recovery-uestc-majie-s001-48848cfce97c；https://mtt.uestc.edu.cn/info/1053/1057.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1587,8 +1641,567 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>管理学</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>学历/学位标签不推明确获授；孤立年月也不补成授位日或学习止期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科；来源department：经济管理学院；来源记载（date_label_as_source）：2000-07</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>经济学</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>学历/学位标签不推明确获授；孤立年月也不补成授位日或学习止期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：经济管理学院；来源记载（date_label_as_source）：2003-02</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>管理学</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>学历/学位标签不推明确获授；孤立年月也不补成授位日或学习止期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：经济管理学院；来源记载（date_label_as_source）：2006-07</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚维多利亚大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>访问学者属非学位经历，不推导师。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>亚利桑那大学</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>同一亚利桑那访问事件并列两处止期，不拆成两次访问；end保持null。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：社会科学学院；来源教育背景止期：2012-09；来源工作经历止期：2012-08；来源处理说明：unknown; preserved both, no arbitrary selection。规范结束日期仍未知，不任意选择。</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>美国威廉玛丽学院</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>访问学者属非学位经历，不推导师。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2006-09</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：经济与管理学院</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：经济与管理学院</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：经济与管理学院；来源记载（source_end_label）：今</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S15"/>
+  <autoFilter ref="A1:S24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1604,6 +2217,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1706,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1993,8 +2615,112 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>环境合作的地方政府网络结构及其演变：以长三角30个城市为例</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：马捷、锁利铭；来源书目信息（期）：2019.09；来源书目信息（页码）：41-49</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>地方政府区域合作边界拓展的行动与逻辑</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：马捷、位韦、阚艳秋；来源书目信息（期）：2019,1；来源书目信息（页码）：47-55</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2004,6 +2730,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2015,14 +2745,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="58.8" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2204,13 +2934,89 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-majie-s001-48848cfce97c</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/info/1053/1057.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:19:54Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>马捷</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-uestc-majie-s002-0f90a605694c</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://mtt.uestc.edu.cn/szll/xnsz/zm/M.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:20:30Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>uestc</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
